--- a/Gold_Reference_partlist_TI_I26.xlsx
+++ b/Gold_Reference_partlist_TI_I26.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\TEC 13vo semestre\Taller integrador\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\TEC 13vo semestre\Taller integrador\REPOSITORIO\Taller_Integrador_S1_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB0F6BE-D1F5-4693-A845-7944F4B14D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B485E35-91C9-451E-80EF-FFC5EC5B8256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="71">
   <si>
     <t>Available inventory  for Taller Integrador, I 2026</t>
   </si>
@@ -234,6 +234,21 @@
   </si>
   <si>
     <t>Siwa On Adapter</t>
+  </si>
+  <si>
+    <t>Hay que cambiarlo</t>
+  </si>
+  <si>
+    <t>Es el mismo??</t>
+  </si>
+  <si>
+    <t>Similar, verificar footprint</t>
+  </si>
+  <si>
+    <t>Excepción</t>
+  </si>
+  <si>
+    <t>??</t>
   </si>
 </sst>
 </file>
@@ -255,7 +270,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -274,6 +289,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -388,7 +409,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -399,16 +420,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -723,20 +750,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" customWidth="1"/>
     <col min="2" max="2" width="30.109375" customWidth="1"/>
     <col min="3" max="3" width="21.44140625" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" customWidth="1"/>
+    <col min="6" max="6" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F1" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -744,158 +776,170 @@
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
+      <c r="F2" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="10"/>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="9"/>
       <c r="B4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="10"/>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="9"/>
       <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="10"/>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
       <c r="B7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="10"/>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
       <c r="B10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="15" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="15" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="16">
         <v>61204021621</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="10"/>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
       <c r="B14" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="10"/>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
       <c r="B15" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="16">
         <v>61200821621</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="10"/>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="9"/>
       <c r="B16" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>35</v>
       </c>
+      <c r="D16" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="10"/>
+      <c r="A17" s="9"/>
       <c r="B17" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="9" t="s">
         <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
@@ -906,8 +950,8 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="10"/>
-      <c r="B19" s="8" t="s">
+      <c r="A19" s="9"/>
+      <c r="B19" s="17" t="s">
         <v>41</v>
       </c>
       <c r="C19" s="5" t="s">
@@ -915,7 +959,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="10"/>
+      <c r="A20" s="9"/>
       <c r="B20" s="5" t="s">
         <v>43</v>
       </c>
@@ -924,7 +968,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="10"/>
+      <c r="A21" s="9"/>
       <c r="B21" s="5" t="s">
         <v>45</v>
       </c>
@@ -933,7 +977,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="10"/>
+      <c r="A22" s="9"/>
       <c r="B22" s="5" t="s">
         <v>47</v>
       </c>
@@ -942,7 +986,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="10"/>
+      <c r="A23" s="9"/>
       <c r="B23" s="5" t="s">
         <v>49</v>
       </c>
@@ -951,7 +995,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="10"/>
+      <c r="A24" s="9"/>
       <c r="B24" s="5" t="s">
         <v>51</v>
       </c>
@@ -960,7 +1004,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="10"/>
+      <c r="A25" s="9"/>
       <c r="B25" s="5" t="s">
         <v>53</v>
       </c>
@@ -969,7 +1013,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="10"/>
+      <c r="A26" s="9"/>
       <c r="B26" s="5" t="s">
         <v>55</v>
       </c>
@@ -978,7 +1022,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="10"/>
+      <c r="A27" s="9"/>
       <c r="B27" s="5" t="s">
         <v>57</v>
       </c>
@@ -993,7 +1037,7 @@
       <c r="B28" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="15" t="s">
         <v>61</v>
       </c>
     </row>
